--- a/XLibur.Tests/Resource/Other/InlinedRichText/ChangeRichTextToFormula/output.xlsx
+++ b/XLibur.Tests/Resource/Other/InlinedRichText/ChangeRichTextToFormula/output.xlsx
@@ -367,7 +367,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="0">
+      <x:c r="A1" s="0" t="str">
         <x:f>1 + 2</x:f>
       </x:c>
     </x:row>
